--- a/Inputs/BEV_parameters.xlsx
+++ b/Inputs/BEV_parameters.xlsx
@@ -466,10 +466,10 @@
         <v>0.9</v>
       </c>
       <c r="F2" s="3">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H2" s="3">
         <v>2.5</v>
@@ -532,7 +532,7 @@
         <v>0.9</v>
       </c>
       <c r="F4" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3">
         <v>22</v>
@@ -565,10 +565,10 @@
         <v>0.9</v>
       </c>
       <c r="F5" s="3">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G5" s="3">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H5" s="3">
         <v>2.5</v>
@@ -598,7 +598,7 @@
         <v>0.9</v>
       </c>
       <c r="F6" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G6" s="3">
         <v>22</v>

--- a/Inputs/BEV_parameters.xlsx
+++ b/Inputs/BEV_parameters.xlsx
@@ -502,7 +502,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="3">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H3" s="3">
         <v>2.5</v>
@@ -532,7 +532,7 @@
         <v>0.9</v>
       </c>
       <c r="F4" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G4" s="3">
         <v>22</v>

--- a/Inputs/BEV_parameters.xlsx
+++ b/Inputs/BEV_parameters.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>charger_id</t>
   </si>
@@ -48,13 +48,19 @@
     <t>TR03</t>
   </si>
   <si>
+    <t>battery_size</t>
+  </si>
+  <si>
     <t>TR04</t>
   </si>
   <si>
     <t>TR05</t>
   </si>
   <si>
-    <t>battery_size</t>
+    <t>TR06</t>
+  </si>
+  <si>
+    <t>TR07</t>
   </si>
 </sst>
 </file>
@@ -439,7 +445,7 @@
         <v>5</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -457,7 +463,7 @@
         <v>0.95</v>
       </c>
       <c r="C2" s="3">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="D2" s="3">
         <v>0.2</v>
@@ -466,13 +472,13 @@
         <v>0.9</v>
       </c>
       <c r="F2" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3">
         <v>6</v>
       </c>
       <c r="H2" s="3">
-        <v>2.5</v>
+        <v>0.85</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -490,7 +496,7 @@
         <v>0.95</v>
       </c>
       <c r="C3" s="3">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="D3" s="3">
         <v>0.15</v>
@@ -499,13 +505,13 @@
         <v>0.9</v>
       </c>
       <c r="F3" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H3" s="3">
-        <v>2.5</v>
+        <v>0.85</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -523,7 +529,7 @@
         <v>0.95</v>
       </c>
       <c r="C4" s="3">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="D4" s="3">
         <v>0.25</v>
@@ -535,10 +541,10 @@
         <v>16</v>
       </c>
       <c r="G4" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H4" s="3">
-        <v>2.5</v>
+        <v>0.85</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -550,13 +556,13 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="3">
         <v>0.95</v>
       </c>
       <c r="C5" s="3">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="D5" s="3">
         <v>0.1</v>
@@ -565,13 +571,13 @@
         <v>0.9</v>
       </c>
       <c r="F5" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G5" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H5" s="3">
-        <v>2.5</v>
+        <v>0.85</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -583,28 +589,28 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="3">
         <v>0.95</v>
       </c>
       <c r="C6" s="3">
-        <v>1</v>
+        <v>0.35</v>
       </c>
       <c r="D6" s="3">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3">
         <v>0.9</v>
       </c>
       <c r="F6" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H6" s="3">
-        <v>2.5</v>
+        <v>0.85</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -615,14 +621,30 @@
       <c r="Q6" s="2"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F7" s="3">
+        <v>23</v>
+      </c>
+      <c r="G7" s="3">
+        <v>6</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0.85</v>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -632,14 +654,30 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.95</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.35</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F8" s="3">
+        <v>7</v>
+      </c>
+      <c r="G8" s="3">
+        <v>11</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0.85</v>
+      </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>

--- a/Inputs/BEV_parameters.xlsx
+++ b/Inputs/BEV_parameters.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>charger_id</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>TR06</t>
-  </si>
-  <si>
-    <t>TR07</t>
   </si>
 </sst>
 </file>
@@ -472,10 +469,10 @@
         <v>0.9</v>
       </c>
       <c r="F2" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G2" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" s="3">
         <v>0.85</v>
@@ -505,10 +502,10 @@
         <v>0.9</v>
       </c>
       <c r="F3" s="3">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H3" s="3">
         <v>0.85</v>
@@ -538,10 +535,10 @@
         <v>0.9</v>
       </c>
       <c r="F4" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G4" s="3">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H4" s="3">
         <v>0.85</v>
@@ -571,10 +568,10 @@
         <v>0.9</v>
       </c>
       <c r="F5" s="3">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G5" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H5" s="3">
         <v>0.85</v>
@@ -598,16 +595,16 @@
         <v>0.35</v>
       </c>
       <c r="D6" s="3">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="E6" s="3">
         <v>0.9</v>
       </c>
       <c r="F6" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G6" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H6" s="3">
         <v>0.85</v>
@@ -631,16 +628,16 @@
         <v>0.35</v>
       </c>
       <c r="D7" s="3">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="E7" s="3">
         <v>0.9</v>
       </c>
       <c r="F7" s="3">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G7" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H7" s="3">
         <v>0.85</v>
@@ -654,30 +651,14 @@
       <c r="Q7" s="2"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="F8" s="3">
-        <v>7</v>
-      </c>
-      <c r="G8" s="3">
-        <v>11</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.85</v>
-      </c>
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>

--- a/Inputs/BEV_parameters.xlsx
+++ b/Inputs/BEV_parameters.xlsx
@@ -8,15 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="helper" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
   <si>
     <t>charger_id</t>
   </si>
@@ -58,13 +57,130 @@
   </si>
   <si>
     <t>TR06</t>
+  </si>
+  <si>
+    <t>TR07</t>
+  </si>
+  <si>
+    <t>TR08</t>
+  </si>
+  <si>
+    <t>TR09</t>
+  </si>
+  <si>
+    <t>TR10</t>
+  </si>
+  <si>
+    <t>BIG</t>
+  </si>
+  <si>
+    <t>TR11</t>
+  </si>
+  <si>
+    <t>TR12</t>
+  </si>
+  <si>
+    <t>TR13</t>
+  </si>
+  <si>
+    <t>TR14</t>
+  </si>
+  <si>
+    <t>TR15</t>
+  </si>
+  <si>
+    <t>TR16</t>
+  </si>
+  <si>
+    <t>TR17</t>
+  </si>
+  <si>
+    <t>TR18</t>
+  </si>
+  <si>
+    <t>TR19</t>
+  </si>
+  <si>
+    <t>TR20</t>
+  </si>
+  <si>
+    <t>TR21</t>
+  </si>
+  <si>
+    <t>TR22</t>
+  </si>
+  <si>
+    <t>TR23</t>
+  </si>
+  <si>
+    <t>TR24</t>
+  </si>
+  <si>
+    <t>TR25</t>
+  </si>
+  <si>
+    <t>TR26</t>
+  </si>
+  <si>
+    <t>TR27</t>
+  </si>
+  <si>
+    <t>TR30</t>
+  </si>
+  <si>
+    <t>TR28</t>
+  </si>
+  <si>
+    <t>TR29</t>
+  </si>
+  <si>
+    <t>TR31</t>
+  </si>
+  <si>
+    <t>TR32</t>
+  </si>
+  <si>
+    <t>TR33</t>
+  </si>
+  <si>
+    <t>TR34</t>
+  </si>
+  <si>
+    <t>TR35</t>
+  </si>
+  <si>
+    <t>TR36</t>
+  </si>
+  <si>
+    <t>TR37</t>
+  </si>
+  <si>
+    <t>TR38</t>
+  </si>
+  <si>
+    <t>TR39</t>
+  </si>
+  <si>
+    <t>TR40</t>
+  </si>
+  <si>
+    <t>bus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery size </t>
+  </si>
+  <si>
+    <t>1000kWh</t>
+  </si>
+  <si>
+    <t>1MW</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,13 +196,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -101,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -115,6 +250,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,23 +567,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="30.88671875" customWidth="1"/>
+    <col min="12" max="12" width="56.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -443,6 +598,9 @@
       </c>
       <c r="H1" s="4" t="s">
         <v>10</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -451,97 +609,115 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
       <c r="Q1" s="1"/>
+      <c r="R1" s="4"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C2" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.9</v>
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C2" s="7">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
       </c>
       <c r="F2" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3">
         <v>16</v>
       </c>
-      <c r="G2" s="3">
-        <v>8</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.85</v>
+      <c r="H2" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I2">
+        <v>18</v>
       </c>
       <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
+      <c r="L2" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0.9</v>
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C3" s="7">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
       </c>
       <c r="F3" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="G3" s="3">
-        <v>8</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.85</v>
+        <v>18</v>
+      </c>
+      <c r="H3" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I3">
+        <v>18</v>
       </c>
       <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="L3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.9</v>
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C4" s="7">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
       </c>
       <c r="F4" s="3">
+        <v>8</v>
+      </c>
+      <c r="G4" s="3">
+        <v>20</v>
+      </c>
+      <c r="H4" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I4">
         <v>18</v>
-      </c>
-      <c r="G4" s="3">
-        <v>9</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.85</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -552,321 +728,2373 @@
       <c r="Q4" s="2"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0.9</v>
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C5" s="7">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
       </c>
       <c r="F5" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G5" s="3">
-        <v>7</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.85</v>
-      </c>
-      <c r="L5" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="H5" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I5">
+        <v>18</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="7"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C6" s="7">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
         <v>12</v>
       </c>
-      <c r="B6" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="F6" s="3">
-        <v>17</v>
-      </c>
       <c r="G6" s="3">
-        <v>9</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.85</v>
+        <v>23</v>
+      </c>
+      <c r="H6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I6">
+        <v>18</v>
       </c>
       <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+    </row>
+    <row r="7" spans="1:18" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C7" s="7">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
         <v>13</v>
       </c>
-      <c r="B7" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0.35</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
+        <v>2</v>
+      </c>
+      <c r="H7" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I7">
         <v>18</v>
-      </c>
-      <c r="G7" s="3">
-        <v>9</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.85</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C8" s="7">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>14</v>
+      </c>
+      <c r="G8" s="3">
+        <v>4</v>
+      </c>
+      <c r="H8" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I8">
+        <v>18</v>
+      </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C9" s="7">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>15</v>
+      </c>
+      <c r="G9" s="3">
+        <v>5</v>
+      </c>
+      <c r="H9" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I9">
+        <v>18</v>
+      </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C10" s="7">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>16</v>
+      </c>
+      <c r="G10" s="3">
+        <v>6</v>
+      </c>
+      <c r="H10" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I10">
+        <v>18</v>
+      </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C11" s="7">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>17</v>
+      </c>
+      <c r="G11" s="3">
+        <v>7</v>
+      </c>
+      <c r="H11" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I11">
+        <v>18</v>
+      </c>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C12" s="7">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>18</v>
+      </c>
+      <c r="G12" s="3">
+        <v>8</v>
+      </c>
+      <c r="H12" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I12">
+        <v>18</v>
+      </c>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C13" s="7">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3">
+        <v>8</v>
+      </c>
+      <c r="G13" s="3">
+        <v>20</v>
+      </c>
+      <c r="H13" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I13">
+        <v>18</v>
+      </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C14" s="7">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3">
+        <v>10</v>
+      </c>
+      <c r="G14" s="3">
+        <v>22</v>
+      </c>
+      <c r="H14" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="I14">
+        <v>18</v>
+      </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B15" s="2"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="10"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-    </row>
-    <row r="17" spans="11:17" x14ac:dyDescent="0.3">
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-    </row>
-    <row r="18" spans="11:17" x14ac:dyDescent="0.3">
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-    </row>
-    <row r="19" spans="11:17" x14ac:dyDescent="0.3">
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-    </row>
-    <row r="20" spans="11:17" x14ac:dyDescent="0.3">
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-    </row>
-    <row r="21" spans="11:17" x14ac:dyDescent="0.3">
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-    </row>
-    <row r="22" spans="11:17" x14ac:dyDescent="0.3">
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-    </row>
-    <row r="23" spans="11:17" x14ac:dyDescent="0.3">
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-    </row>
-    <row r="24" spans="11:17" x14ac:dyDescent="0.3">
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-    </row>
-    <row r="25" spans="11:17" x14ac:dyDescent="0.3">
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="10"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="10"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="10"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="10"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="10"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="10"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="10"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="10"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C26" s="2"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C27" s="2"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="C28" s="2"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="2"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S75"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C3" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>8</v>
+      </c>
+      <c r="H3" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3">
+        <v>10</v>
+      </c>
+      <c r="H4" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="3"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="3"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>6</v>
+      </c>
+      <c r="G6" s="3">
+        <v>14</v>
+      </c>
+      <c r="H6" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="3"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3">
+        <v>16</v>
+      </c>
+      <c r="H7" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>21</v>
+      </c>
+      <c r="G8" s="2">
+        <v>7</v>
+      </c>
+      <c r="H8" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>22</v>
+      </c>
+      <c r="G9" s="2">
+        <v>8</v>
+      </c>
+      <c r="H9" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>23</v>
+      </c>
+      <c r="G10" s="2">
+        <v>9</v>
+      </c>
+      <c r="H10" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>18</v>
+      </c>
+      <c r="G11" s="2">
+        <v>7</v>
+      </c>
+      <c r="H11" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>19</v>
+      </c>
+      <c r="G12" s="2">
+        <v>6</v>
+      </c>
+      <c r="H12" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>14</v>
+      </c>
+      <c r="G13" s="2">
+        <v>22</v>
+      </c>
+      <c r="H13" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2">
+        <v>15</v>
+      </c>
+      <c r="G14" s="2">
+        <v>23</v>
+      </c>
+      <c r="H14" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D15" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2">
+        <v>21</v>
+      </c>
+      <c r="H15" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2">
+        <v>20</v>
+      </c>
+      <c r="G16" s="2">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C17" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2">
+        <v>18</v>
+      </c>
+      <c r="G17" s="2">
+        <v>5</v>
+      </c>
+      <c r="H17" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="3"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C18" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2">
+        <v>17</v>
+      </c>
+      <c r="G18" s="2">
+        <v>6</v>
+      </c>
+      <c r="H18" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C19" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2">
+        <v>21</v>
+      </c>
+      <c r="G19" s="2">
+        <v>9</v>
+      </c>
+      <c r="H19" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D20" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E20" s="2">
+        <v>1</v>
+      </c>
+      <c r="F20" s="2">
+        <v>22</v>
+      </c>
+      <c r="G20" s="2">
+        <v>7</v>
+      </c>
+      <c r="H20" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D21" s="2">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>23</v>
+      </c>
+      <c r="G21" s="2">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>16</v>
+      </c>
+      <c r="G22" s="2">
+        <v>6</v>
+      </c>
+      <c r="H22" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>17</v>
+      </c>
+      <c r="G23" s="2">
+        <v>5</v>
+      </c>
+      <c r="H23" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C24" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D24" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>18</v>
+      </c>
+      <c r="G24" s="2">
+        <v>6</v>
+      </c>
+      <c r="H24" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C25" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>19</v>
+      </c>
+      <c r="G25" s="2">
+        <v>7</v>
+      </c>
+      <c r="H25" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="2"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C26" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>15</v>
+      </c>
+      <c r="G26" s="2">
+        <v>22</v>
+      </c>
+      <c r="H26" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="2"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27">
+        <v>0.95</v>
+      </c>
+      <c r="C27" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D27">
+        <v>0.12</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>14</v>
+      </c>
+      <c r="G27">
+        <v>23</v>
+      </c>
+      <c r="H27" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="2"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28">
+        <v>0.95</v>
+      </c>
+      <c r="C28" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D28">
+        <v>0.08</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>13</v>
+      </c>
+      <c r="G28">
+        <v>21</v>
+      </c>
+      <c r="H28" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="M28" s="2"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="2"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29">
+        <v>0.95</v>
+      </c>
+      <c r="C29" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D29">
+        <v>0.1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>20</v>
+      </c>
+      <c r="G29">
+        <v>9</v>
+      </c>
+      <c r="H29" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="2"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C30" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D30" s="2">
+        <v>0.11</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>22</v>
+      </c>
+      <c r="G30" s="2">
+        <v>8</v>
+      </c>
+      <c r="H30" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="2"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C31" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D31" s="2">
+        <v>0.09</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>23</v>
+      </c>
+      <c r="G31" s="2">
+        <v>9</v>
+      </c>
+      <c r="H31" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="2"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C32" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>18</v>
+      </c>
+      <c r="G32" s="2">
+        <v>7</v>
+      </c>
+      <c r="H32" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="2"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C33" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>19</v>
+      </c>
+      <c r="G33" s="2">
+        <v>6</v>
+      </c>
+      <c r="H33" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C34" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>14</v>
+      </c>
+      <c r="G34" s="2">
+        <v>22</v>
+      </c>
+      <c r="H34" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="3"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C35" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>15</v>
+      </c>
+      <c r="G35" s="2">
+        <v>23</v>
+      </c>
+      <c r="H35" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="3"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C36" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="E36" s="2">
+        <v>1</v>
+      </c>
+      <c r="F36" s="2">
+        <v>13</v>
+      </c>
+      <c r="G36" s="2">
+        <v>21</v>
+      </c>
+      <c r="H36" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="3"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C37" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1</v>
+      </c>
+      <c r="F37" s="2">
+        <v>20</v>
+      </c>
+      <c r="G37" s="2">
+        <v>8</v>
+      </c>
+      <c r="H37" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="3"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C38" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1</v>
+      </c>
+      <c r="F38" s="2">
+        <v>18</v>
+      </c>
+      <c r="G38" s="2">
+        <v>5</v>
+      </c>
+      <c r="H38" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="3"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C39" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D39" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1</v>
+      </c>
+      <c r="F39" s="2">
+        <v>17</v>
+      </c>
+      <c r="G39" s="2">
+        <v>6</v>
+      </c>
+      <c r="H39" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="3"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C40" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D40" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E40" s="2">
+        <v>1</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3">
+        <v>8</v>
+      </c>
+      <c r="H40" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="M40" s="2"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C41" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D41" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3">
+        <v>2</v>
+      </c>
+      <c r="G41" s="3">
+        <v>10</v>
+      </c>
+      <c r="H41" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="C42" s="2">
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="D42" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="E42" s="2">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3">
+        <v>4</v>
+      </c>
+      <c r="G42" s="3">
+        <v>12</v>
+      </c>
+      <c r="H42" s="2">
+        <v>8.4999999999999992E-2</v>
+      </c>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="2"/>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="2"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="2"/>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="2"/>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="2"/>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="2"/>
+    </row>
+    <row r="49" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="N49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="2"/>
+    </row>
+    <row r="50" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="N50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="2"/>
+    </row>
+    <row r="51" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="N51" s="2"/>
+      <c r="Q51" s="2"/>
+      <c r="R51" s="2"/>
+      <c r="S51" s="2"/>
+    </row>
+    <row r="52" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="2"/>
+    </row>
+    <row r="53" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="2"/>
+      <c r="R53" s="2"/>
+      <c r="S53" s="2"/>
+    </row>
+    <row r="54" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="2"/>
+      <c r="R54" s="2"/>
+      <c r="S54" s="2"/>
+    </row>
+    <row r="55" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="2"/>
+      <c r="R55" s="2"/>
+      <c r="S55" s="2"/>
+    </row>
+    <row r="56" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
+    </row>
+    <row r="57" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="2"/>
+    </row>
+    <row r="58" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="2"/>
+    </row>
+    <row r="59" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="2"/>
+      <c r="S59" s="2"/>
+    </row>
+    <row r="60" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="2"/>
+    </row>
+    <row r="61" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="2"/>
+    </row>
+    <row r="62" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="2"/>
+    </row>
+    <row r="63" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="2"/>
+      <c r="R63" s="2"/>
+      <c r="S63" s="2"/>
+    </row>
+    <row r="64" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="2"/>
+      <c r="R64" s="2"/>
+      <c r="S64" s="2"/>
+    </row>
+    <row r="65" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="2"/>
+      <c r="R65" s="2"/>
+      <c r="S65" s="2"/>
+    </row>
+    <row r="66" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L66" s="2"/>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="2"/>
+      <c r="R66" s="2"/>
+      <c r="S66" s="2"/>
+    </row>
+    <row r="67" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="2"/>
+      <c r="R67" s="2"/>
+      <c r="S67" s="2"/>
+    </row>
+    <row r="68" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+    </row>
+    <row r="69" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="2"/>
+      <c r="R69" s="2"/>
+      <c r="S69" s="2"/>
+    </row>
+    <row r="70" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="2"/>
+      <c r="R70" s="2"/>
+      <c r="S70" s="2"/>
+    </row>
+    <row r="71" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="2"/>
+      <c r="R71" s="2"/>
+      <c r="S71" s="2"/>
+    </row>
+    <row r="72" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="2"/>
+      <c r="R72" s="2"/>
+      <c r="S72" s="2"/>
+    </row>
+    <row r="73" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="2"/>
+      <c r="R73" s="2"/>
+      <c r="S73" s="2"/>
+    </row>
+    <row r="74" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="2"/>
+      <c r="R74" s="2"/>
+      <c r="S74" s="2"/>
+    </row>
+    <row r="75" spans="12:19" x14ac:dyDescent="0.3">
+      <c r="L75" s="2"/>
+      <c r="M75" s="2"/>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="2"/>
+      <c r="R75" s="2"/>
+      <c r="S75" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>